--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/138.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/138.xlsx
@@ -426,13 +426,13 @@
         <v>-16.48829704161824</v>
       </c>
       <c r="E2">
-        <v>-13.792253093071</v>
+        <v>-16.19714449958442</v>
       </c>
       <c r="F2">
-        <v>-2.172966314514782</v>
+        <v>-3.040952766707427</v>
       </c>
       <c r="G2">
-        <v>-10.68407842192069</v>
+        <v>-14.13285579018414</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.02461589453477</v>
       </c>
       <c r="E3">
-        <v>-14.253342316532</v>
+        <v>-16.59774236725096</v>
       </c>
       <c r="F3">
-        <v>-1.635771684291806</v>
+        <v>-3.226640701586787</v>
       </c>
       <c r="G3">
-        <v>-10.90804013819792</v>
+        <v>-14.09248368733273</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.51412078170193</v>
       </c>
       <c r="E4">
-        <v>-14.74246279410047</v>
+        <v>-18.23134860925197</v>
       </c>
       <c r="F4">
-        <v>-1.758131970730489</v>
+        <v>-2.789489565895078</v>
       </c>
       <c r="G4">
-        <v>-9.857421958582513</v>
+        <v>-13.04074654332505</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.98984457490299</v>
       </c>
       <c r="E5">
-        <v>-14.5155364331021</v>
+        <v>-17.12216682818323</v>
       </c>
       <c r="F5">
-        <v>-1.647905247162946</v>
+        <v>-3.32761620704929</v>
       </c>
       <c r="G5">
-        <v>-9.916379464091394</v>
+        <v>-13.68193300337109</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.44427558283746</v>
       </c>
       <c r="E6">
-        <v>-14.28637300594395</v>
+        <v>-17.82100093704692</v>
       </c>
       <c r="F6">
-        <v>-1.296798437562978</v>
+        <v>-3.090613033097861</v>
       </c>
       <c r="G6">
-        <v>-10.11868028090518</v>
+        <v>-12.13374976083984</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.87546773505811</v>
       </c>
       <c r="E7">
-        <v>-15.31299164890484</v>
+        <v>-18.08072250680884</v>
       </c>
       <c r="F7">
-        <v>-1.375376382116379</v>
+        <v>-2.507561406240379</v>
       </c>
       <c r="G7">
-        <v>-10.1495610496955</v>
+        <v>-12.56531578788477</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.28494918429127</v>
       </c>
       <c r="E8">
-        <v>-16.06851772387055</v>
+        <v>-20.18775806394175</v>
       </c>
       <c r="F8">
-        <v>-1.401946216259707</v>
+        <v>-3.331927054551116</v>
       </c>
       <c r="G8">
-        <v>-9.402440442938317</v>
+        <v>-11.83472142445963</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.68184290749579</v>
       </c>
       <c r="E9">
-        <v>-17.72029673206435</v>
+        <v>-21.07710960278214</v>
       </c>
       <c r="F9">
-        <v>-1.428579398639652</v>
+        <v>-2.5316123561252</v>
       </c>
       <c r="G9">
-        <v>-8.755172510736633</v>
+        <v>-12.39398843513641</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.07370661889572</v>
       </c>
       <c r="E10">
-        <v>-18.10364111376166</v>
+        <v>-18.61353823007732</v>
       </c>
       <c r="F10">
-        <v>-1.194627234134317</v>
+        <v>-2.025393429902304</v>
       </c>
       <c r="G10">
-        <v>-8.884452624590711</v>
+        <v>-10.22188653809196</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.48926687862931</v>
       </c>
       <c r="E11">
-        <v>-17.54829623230501</v>
+        <v>-20.63047073987962</v>
       </c>
       <c r="F11">
-        <v>-0.9508608440710045</v>
+        <v>-2.147170120711147</v>
       </c>
       <c r="G11">
-        <v>-8.792972319704031</v>
+        <v>-11.75058390957906</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.94930058178525</v>
       </c>
       <c r="E12">
-        <v>-17.8352746871191</v>
+        <v>-20.4617850830939</v>
       </c>
       <c r="F12">
-        <v>-0.8311873147178649</v>
+        <v>-2.268864458812387</v>
       </c>
       <c r="G12">
-        <v>-8.326751501954009</v>
+        <v>-11.6731668021432</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.47751327322249</v>
       </c>
       <c r="E13">
-        <v>-19.02388137380837</v>
+        <v>-22.24430113588913</v>
       </c>
       <c r="F13">
-        <v>-0.8726194370246341</v>
+        <v>-2.894561326707866</v>
       </c>
       <c r="G13">
-        <v>-7.331326737569331</v>
+        <v>-10.57510188385896</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.10880846602421</v>
       </c>
       <c r="E14">
-        <v>-18.00786388849943</v>
+        <v>-21.90891329393305</v>
       </c>
       <c r="F14">
-        <v>-0.5919162738955269</v>
+        <v>-1.676741364471267</v>
       </c>
       <c r="G14">
-        <v>-7.142119128363364</v>
+        <v>-10.82642194847273</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.857490283109749</v>
       </c>
       <c r="E15">
-        <v>-20.14364619863303</v>
+        <v>-25.28762133647793</v>
       </c>
       <c r="F15">
-        <v>-0.8458864811720161</v>
+        <v>-1.78033552766495</v>
       </c>
       <c r="G15">
-        <v>-6.795124297664655</v>
+        <v>-10.65515087499853</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.738001185206071</v>
       </c>
       <c r="E16">
-        <v>-20.73609739610853</v>
+        <v>-23.83053501129591</v>
       </c>
       <c r="F16">
-        <v>-0.09489709533541878</v>
+        <v>-1.472268301875922</v>
       </c>
       <c r="G16">
-        <v>-7.451698173377231</v>
+        <v>-8.635489668400901</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.744814585475131</v>
       </c>
       <c r="E17">
-        <v>-20.14971888227732</v>
+        <v>-23.31747702012289</v>
       </c>
       <c r="F17">
-        <v>0.04930883050083554</v>
+        <v>-1.523694400362072</v>
       </c>
       <c r="G17">
-        <v>-6.76911996245368</v>
+        <v>-8.723103256097712</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.861607598695812</v>
       </c>
       <c r="E18">
-        <v>-23.01154237311269</v>
+        <v>-26.45643859175368</v>
       </c>
       <c r="F18">
-        <v>0.1754446718419258</v>
+        <v>-1.182648082589933</v>
       </c>
       <c r="G18">
-        <v>-6.835959876891565</v>
+        <v>-9.663539859075097</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.06898085364625</v>
       </c>
       <c r="E19">
-        <v>-24.33351261932785</v>
+        <v>-27.00388581454095</v>
       </c>
       <c r="F19">
-        <v>0.4632721360316372</v>
+        <v>-0.8573612223823327</v>
       </c>
       <c r="G19">
-        <v>-5.536246319264776</v>
+        <v>-8.000884572886928</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.33032492405051</v>
       </c>
       <c r="E20">
-        <v>-23.02634595464377</v>
+        <v>-26.95295406737668</v>
       </c>
       <c r="F20">
-        <v>0.576147607742753</v>
+        <v>-1.076336280045356</v>
       </c>
       <c r="G20">
-        <v>-5.768606889575142</v>
+        <v>-8.653787053596453</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.60944196690673</v>
       </c>
       <c r="E21">
-        <v>-23.18746453136267</v>
+        <v>-26.83083470881183</v>
       </c>
       <c r="F21">
-        <v>0.7165843135002614</v>
+        <v>-0.4740584633744386</v>
       </c>
       <c r="G21">
-        <v>-6.201311744285582</v>
+        <v>-8.111539557537068</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.87654823336278</v>
       </c>
       <c r="E22">
-        <v>-25.16229128984164</v>
+        <v>-29.0735161763705</v>
       </c>
       <c r="F22">
-        <v>1.121344703956445</v>
+        <v>-0.2604387072644733</v>
       </c>
       <c r="G22">
-        <v>-6.654320174788373</v>
+        <v>-7.009329836237658</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.09900007338038</v>
       </c>
       <c r="E23">
-        <v>-24.26323070272881</v>
+        <v>-27.2114348352605</v>
       </c>
       <c r="F23">
-        <v>1.00469050993109</v>
+        <v>-0.2451187280914698</v>
       </c>
       <c r="G23">
-        <v>-5.971139444576674</v>
+        <v>-7.399765645502684</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.25873313303613</v>
       </c>
       <c r="E24">
-        <v>-24.66165037439766</v>
+        <v>-27.67715668763134</v>
       </c>
       <c r="F24">
-        <v>1.296030633841246</v>
+        <v>-0.3875817855677831</v>
       </c>
       <c r="G24">
-        <v>-6.391740944795539</v>
+        <v>-6.338494130341902</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.33811291352055</v>
       </c>
       <c r="E25">
-        <v>-24.53474894728071</v>
+        <v>-28.61880757278631</v>
       </c>
       <c r="F25">
-        <v>1.534701450121633</v>
+        <v>-0.6220066862888763</v>
       </c>
       <c r="G25">
-        <v>-6.743459923978789</v>
+        <v>-7.708914319596445</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.33027054804268</v>
       </c>
       <c r="E26">
-        <v>-25.32156677763943</v>
+        <v>-28.15798552929177</v>
       </c>
       <c r="F26">
-        <v>1.774168870477485</v>
+        <v>0.2205541592843453</v>
       </c>
       <c r="G26">
-        <v>-6.129846997729335</v>
+        <v>-8.031526982398422</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.24048275533505</v>
       </c>
       <c r="E27">
-        <v>-26.19686646163401</v>
+        <v>-28.02693149150979</v>
       </c>
       <c r="F27">
-        <v>1.532139013950452</v>
+        <v>-0.4333770176715878</v>
       </c>
       <c r="G27">
-        <v>-6.038740784488592</v>
+        <v>-8.184007399391714</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.07407988307417</v>
       </c>
       <c r="E28">
-        <v>-25.68576929970632</v>
+        <v>-29.64611227955937</v>
       </c>
       <c r="F28">
-        <v>1.74818500752287</v>
+        <v>-0.02609695110394059</v>
       </c>
       <c r="G28">
-        <v>-6.444040943224945</v>
+        <v>-7.381805935952138</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.84373774995754</v>
       </c>
       <c r="E29">
-        <v>-24.93657403140332</v>
+        <v>-28.16854593067766</v>
       </c>
       <c r="F29">
-        <v>1.35262278102356</v>
+        <v>-0.06827262333800851</v>
       </c>
       <c r="G29">
-        <v>-6.78801655639184</v>
+        <v>-7.246676088130166</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.56779199043862</v>
       </c>
       <c r="E30">
-        <v>-25.76121820514811</v>
+        <v>-28.89211003609723</v>
       </c>
       <c r="F30">
-        <v>1.695867282606328</v>
+        <v>0.1586708506385489</v>
       </c>
       <c r="G30">
-        <v>-6.743559240344967</v>
+        <v>-6.8840389297584</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.2589120252985</v>
       </c>
       <c r="E31">
-        <v>-26.4976612906455</v>
+        <v>-29.55964786109391</v>
       </c>
       <c r="F31">
-        <v>1.845050796134809</v>
+        <v>-0.09054032036204486</v>
       </c>
       <c r="G31">
-        <v>-6.217331474150115</v>
+        <v>-8.119739778837843</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.935878689012556</v>
       </c>
       <c r="E32">
-        <v>-24.36861734983531</v>
+        <v>-28.82040617865978</v>
       </c>
       <c r="F32">
-        <v>1.502846789338484</v>
+        <v>-0.5005023928974888</v>
       </c>
       <c r="G32">
-        <v>-6.482807431489811</v>
+        <v>-8.771543158428329</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.61061732408427</v>
       </c>
       <c r="E33">
-        <v>-24.37177369621866</v>
+        <v>-30.29946918820103</v>
       </c>
       <c r="F33">
-        <v>1.042096059947855</v>
+        <v>0.2013168835295023</v>
       </c>
       <c r="G33">
-        <v>-6.926794625398088</v>
+        <v>-7.808975558520917</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.293333325917777</v>
       </c>
       <c r="E34">
-        <v>-24.17275179205556</v>
+        <v>-27.39710679804899</v>
       </c>
       <c r="F34">
-        <v>1.21971501318805</v>
+        <v>0.1626356583978515</v>
       </c>
       <c r="G34">
-        <v>-7.098188189057236</v>
+        <v>-7.912737987358294</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.999571047424929</v>
       </c>
       <c r="E35">
-        <v>-23.39294856793472</v>
+        <v>-26.21552830301962</v>
       </c>
       <c r="F35">
-        <v>1.338462866433616</v>
+        <v>-0.3209972459120046</v>
       </c>
       <c r="G35">
-        <v>-6.026342791444021</v>
+        <v>-6.831523745868942</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.733197086860049</v>
       </c>
       <c r="E36">
-        <v>-23.85150637442543</v>
+        <v>-26.66841646005273</v>
       </c>
       <c r="F36">
-        <v>1.291395126626755</v>
+        <v>-0.2564944876820714</v>
       </c>
       <c r="G36">
-        <v>-6.349256713890072</v>
+        <v>-8.711678563441687</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.496220790447188</v>
       </c>
       <c r="E37">
-        <v>-23.13699468854718</v>
+        <v>-28.44449755128306</v>
       </c>
       <c r="F37">
-        <v>0.9671994397948922</v>
+        <v>-0.3994128606090734</v>
       </c>
       <c r="G37">
-        <v>-5.846444436294486</v>
+        <v>-8.29831060522613</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.292876655697334</v>
       </c>
       <c r="E38">
-        <v>-22.11083342146107</v>
+        <v>-27.94007536004267</v>
       </c>
       <c r="F38">
-        <v>0.8003797771920781</v>
+        <v>0.116715313526727</v>
       </c>
       <c r="G38">
-        <v>-6.447646127317212</v>
+        <v>-7.826624076790772</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.118444847287858</v>
       </c>
       <c r="E39">
-        <v>-23.05522856186469</v>
+        <v>-24.55230584100845</v>
       </c>
       <c r="F39">
-        <v>1.405048197942352</v>
+        <v>0.6892384634583685</v>
       </c>
       <c r="G39">
-        <v>-6.794286729643219</v>
+        <v>-8.651516019356512</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.975270924384398</v>
       </c>
       <c r="E40">
-        <v>-22.38500082330745</v>
+        <v>-27.22473949189503</v>
       </c>
       <c r="F40">
-        <v>0.9683666310545711</v>
+        <v>-0.2017568601267378</v>
       </c>
       <c r="G40">
-        <v>-7.026524809768633</v>
+        <v>-7.872812808154683</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.859691718632382</v>
       </c>
       <c r="E41">
-        <v>-21.64422398818472</v>
+        <v>-25.6147990550581</v>
       </c>
       <c r="F41">
-        <v>1.144938754684661</v>
+        <v>-0.4484150971916431</v>
       </c>
       <c r="G41">
-        <v>-6.555089882794259</v>
+        <v>-8.326443621218857</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.769700772328352</v>
       </c>
       <c r="E42">
-        <v>-21.77104390276953</v>
+        <v>-25.03279051864429</v>
       </c>
       <c r="F42">
-        <v>1.163783271372475</v>
+        <v>0.2719137421220466</v>
       </c>
       <c r="G42">
-        <v>-6.331247346156437</v>
+        <v>-7.706010971158505</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.709094865435473</v>
       </c>
       <c r="E43">
-        <v>-21.20597638761841</v>
+        <v>-23.93152451014096</v>
       </c>
       <c r="F43">
-        <v>0.819487189061855</v>
+        <v>0.1836577707193947</v>
       </c>
       <c r="G43">
-        <v>-6.701813261094757</v>
+        <v>-7.434807770035869</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.673501274860241</v>
       </c>
       <c r="E44">
-        <v>-19.97171815445782</v>
+        <v>-25.43334763004476</v>
       </c>
       <c r="F44">
-        <v>1.136366154564388</v>
+        <v>0.2713301464922071</v>
       </c>
       <c r="G44">
-        <v>-5.70261116424977</v>
+        <v>-6.661643101521241</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.663655067376155</v>
       </c>
       <c r="E45">
-        <v>-21.05198562898758</v>
+        <v>-23.80416570714924</v>
       </c>
       <c r="F45">
-        <v>1.347789310569639</v>
+        <v>0.3257858743945925</v>
       </c>
       <c r="G45">
-        <v>-5.693811734206387</v>
+        <v>-8.498102028521146</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.681815033815274</v>
       </c>
       <c r="E46">
-        <v>-19.22698796152639</v>
+        <v>-21.56743918291066</v>
       </c>
       <c r="F46">
-        <v>1.016829615772934</v>
+        <v>0.02620493675344716</v>
       </c>
       <c r="G46">
-        <v>-5.471091472506379</v>
+        <v>-8.50081005477227</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.729737637230684</v>
       </c>
       <c r="E47">
-        <v>-20.0979901236877</v>
+        <v>-23.41485732518383</v>
       </c>
       <c r="F47">
-        <v>1.546626755664892</v>
+        <v>-0.6839026645819963</v>
       </c>
       <c r="G47">
-        <v>-6.262603184399649</v>
+        <v>-9.684584997068244</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.815107873988983</v>
       </c>
       <c r="E48">
-        <v>-18.62310236718152</v>
+        <v>-20.91062478436415</v>
       </c>
       <c r="F48">
-        <v>1.068447342674852</v>
+        <v>-0.07201571226914964</v>
       </c>
       <c r="G48">
-        <v>-5.783550692139412</v>
+        <v>-7.284777156741638</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.93567624674926</v>
       </c>
       <c r="E49">
-        <v>-18.39239020191274</v>
+        <v>-22.0535844530561</v>
       </c>
       <c r="F49">
-        <v>0.69756875657358</v>
+        <v>-0.0009667056377474344</v>
       </c>
       <c r="G49">
-        <v>-5.380759926921826</v>
+        <v>-8.7281518380451</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.093030613303259</v>
       </c>
       <c r="E50">
-        <v>-18.1862631220316</v>
+        <v>-20.2194347396254</v>
       </c>
       <c r="F50">
-        <v>0.6929807605365519</v>
+        <v>-0.3613872897264146</v>
       </c>
       <c r="G50">
-        <v>-6.001013807523058</v>
+        <v>-7.362949068560449</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.287614128562371</v>
       </c>
       <c r="E51">
-        <v>-18.39486274872093</v>
+        <v>-20.49117035092967</v>
       </c>
       <c r="F51">
-        <v>0.6765371420165441</v>
+        <v>-0.2774405821196735</v>
       </c>
       <c r="G51">
-        <v>-5.445686346038013</v>
+        <v>-9.0150569566605</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.511953523939134</v>
       </c>
       <c r="E52">
-        <v>-17.79903783810972</v>
+        <v>-21.34027734126389</v>
       </c>
       <c r="F52">
-        <v>0.543535935532024</v>
+        <v>-0.3909930881096396</v>
       </c>
       <c r="G52">
-        <v>-6.353921272554905</v>
+        <v>-7.988887155852609</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.765017551231727</v>
       </c>
       <c r="E53">
-        <v>-17.78607281702576</v>
+        <v>-21.20206378607579</v>
       </c>
       <c r="F53">
-        <v>0.9973151914828887</v>
+        <v>-0.1868795267570996</v>
       </c>
       <c r="G53">
-        <v>-4.966577574503607</v>
+        <v>-6.955030268302532</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.039136540709624</v>
       </c>
       <c r="E54">
-        <v>-17.19833123251824</v>
+        <v>-20.79733595011426</v>
       </c>
       <c r="F54">
-        <v>0.5859871725953782</v>
+        <v>-0.3911467075834373</v>
       </c>
       <c r="G54">
-        <v>-4.771963844432012</v>
+        <v>-6.507398163755518</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.330070267129866</v>
       </c>
       <c r="E55">
-        <v>-16.53538528016534</v>
+        <v>-18.26785716670181</v>
       </c>
       <c r="F55">
-        <v>0.8866695777007118</v>
+        <v>-0.7014762572726702</v>
       </c>
       <c r="G55">
-        <v>-5.252539187640314</v>
+        <v>-7.177399612175377</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.638384200569501</v>
       </c>
       <c r="E56">
-        <v>-16.0789332140882</v>
+        <v>-19.22714645811666</v>
       </c>
       <c r="F56">
-        <v>0.4709269785739139</v>
+        <v>-0.9898287199733498</v>
       </c>
       <c r="G56">
-        <v>-4.384123502869774</v>
+        <v>-8.657249884230531</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.954942330554058</v>
       </c>
       <c r="E57">
-        <v>-16.38952766085228</v>
+        <v>-18.52373406203121</v>
       </c>
       <c r="F57">
-        <v>0.4075621130442239</v>
+        <v>-1.211671869049235</v>
       </c>
       <c r="G57">
-        <v>-5.457958538352091</v>
+        <v>-8.096291184783185</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.28030061478463</v>
       </c>
       <c r="E58">
-        <v>-15.65690207894336</v>
+        <v>-18.69807125437851</v>
       </c>
       <c r="F58">
-        <v>0.8618671593590146</v>
+        <v>-0.3517781540844858</v>
       </c>
       <c r="G58">
-        <v>-5.91119870704263</v>
+        <v>-9.744823683700822</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.61294029032893</v>
       </c>
       <c r="E59">
-        <v>-15.86062001065241</v>
+        <v>-19.39439206016794</v>
       </c>
       <c r="F59">
-        <v>1.049031108151564</v>
+        <v>-1.063644460839025</v>
       </c>
       <c r="G59">
-        <v>-5.851671787700995</v>
+        <v>-7.403046396132102</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.94414813198009</v>
       </c>
       <c r="E60">
-        <v>-15.91924563515572</v>
+        <v>-16.78183842108478</v>
       </c>
       <c r="F60">
-        <v>0.507510585220565</v>
+        <v>-0.6784642184683772</v>
       </c>
       <c r="G60">
-        <v>-5.740331520124227</v>
+        <v>-7.56085679144362</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.27293290529319</v>
       </c>
       <c r="E61">
-        <v>-15.51792774012196</v>
+        <v>-17.12512392171024</v>
       </c>
       <c r="F61">
-        <v>0.5655890404045182</v>
+        <v>-1.267893429047335</v>
       </c>
       <c r="G61">
-        <v>-5.871495334390151</v>
+        <v>-6.849370896871153</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.58853641858269</v>
       </c>
       <c r="E62">
-        <v>-15.89504094158472</v>
+        <v>-18.49100225190377</v>
       </c>
       <c r="F62">
-        <v>0.902343515145816</v>
+        <v>-1.158787969267923</v>
       </c>
       <c r="G62">
-        <v>-5.865887270246626</v>
+        <v>-8.141327846299429</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.88553825104267</v>
       </c>
       <c r="E63">
-        <v>-14.82238130338784</v>
+        <v>-17.74605469221997</v>
       </c>
       <c r="F63">
-        <v>0.3995390588766076</v>
+        <v>-1.152397715899125</v>
       </c>
       <c r="G63">
-        <v>-6.176002623637854</v>
+        <v>-8.524606256108552</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.16205997834155</v>
       </c>
       <c r="E64">
-        <v>-15.79320461810023</v>
+        <v>-16.86398493958392</v>
       </c>
       <c r="F64">
-        <v>0.267553007883884</v>
+        <v>-0.4045361492455201</v>
       </c>
       <c r="G64">
-        <v>-5.855720584895524</v>
+        <v>-9.281003011466771</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.40729066309656</v>
       </c>
       <c r="E65">
-        <v>-14.75760601118212</v>
+        <v>-18.08957567349383</v>
       </c>
       <c r="F65">
-        <v>0.5031815251007113</v>
+        <v>-1.298038479294767</v>
       </c>
       <c r="G65">
-        <v>-6.526748302432558</v>
+        <v>-8.852721045596798</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.62082511532866</v>
       </c>
       <c r="E66">
-        <v>-14.18791492406918</v>
+        <v>-17.02696019064597</v>
       </c>
       <c r="F66">
-        <v>0.2525854032770658</v>
+        <v>-1.101055553826493</v>
       </c>
       <c r="G66">
-        <v>-5.472240231808507</v>
+        <v>-8.887647301036109</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.80360120593898</v>
       </c>
       <c r="E67">
-        <v>-14.81254545784318</v>
+        <v>-16.30954575292881</v>
       </c>
       <c r="F67">
-        <v>0.4313968870715875</v>
+        <v>-1.159774618053242</v>
       </c>
       <c r="G67">
-        <v>-5.891332123261463</v>
+        <v>-7.493675890815189</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.95112168736268</v>
       </c>
       <c r="E68">
-        <v>-15.1160166149932</v>
+        <v>-16.27403798823466</v>
       </c>
       <c r="F68">
-        <v>0.3063838932245438</v>
+        <v>-0.9198788052472626</v>
       </c>
       <c r="G68">
-        <v>-5.703200441355761</v>
+        <v>-7.556900689524191</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.06834070048814</v>
       </c>
       <c r="E69">
-        <v>-14.71031062864601</v>
+        <v>-18.11843563834472</v>
       </c>
       <c r="F69">
-        <v>0.5624469678682863</v>
+        <v>-0.6269066723912461</v>
       </c>
       <c r="G69">
-        <v>-5.695990073171228</v>
+        <v>-7.993968843255391</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.15391481904425</v>
       </c>
       <c r="E70">
-        <v>-14.11718468854337</v>
+        <v>-17.10315176582502</v>
       </c>
       <c r="F70">
-        <v>-0.05845760592707253</v>
+        <v>-0.7928972649473277</v>
       </c>
       <c r="G70">
-        <v>-6.512291150062561</v>
+        <v>-7.432225544515238</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.21087597473985</v>
       </c>
       <c r="E71">
-        <v>-15.1912889099487</v>
+        <v>-17.36081740838746</v>
       </c>
       <c r="F71">
-        <v>0.07580106305430662</v>
+        <v>-1.451534424030989</v>
       </c>
       <c r="G71">
-        <v>-4.752613705754971</v>
+        <v>-7.699118415345742</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.24659324096805</v>
       </c>
       <c r="E72">
-        <v>-15.13397654290762</v>
+        <v>-16.1878022577066</v>
       </c>
       <c r="F72">
-        <v>0.1541873791919398</v>
+        <v>-1.571371866946377</v>
       </c>
       <c r="G72">
-        <v>-5.202444012540062</v>
+        <v>-7.263434069649957</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.25815613525017</v>
       </c>
       <c r="E73">
-        <v>-14.74417455727537</v>
+        <v>-16.89168561508884</v>
       </c>
       <c r="F73">
-        <v>0.4202238418381622</v>
+        <v>-1.348557906144328</v>
       </c>
       <c r="G73">
-        <v>-4.822635054456097</v>
+        <v>-7.187824520078543</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.24719312069927</v>
       </c>
       <c r="E74">
-        <v>-14.70918756709211</v>
+        <v>-16.32432669208984</v>
       </c>
       <c r="F74">
-        <v>-0.1408736617665414</v>
+        <v>-1.411121416480805</v>
       </c>
       <c r="G74">
-        <v>-4.880483527209321</v>
+        <v>-8.224501992428079</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.21860174250928</v>
       </c>
       <c r="E75">
-        <v>-15.8128491383455</v>
+        <v>-17.8272502311775</v>
       </c>
       <c r="F75">
-        <v>0.03261815385801921</v>
+        <v>-1.37816132896868</v>
       </c>
       <c r="G75">
-        <v>-4.950998147195797</v>
+        <v>-6.764071380506291</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.16805348524737</v>
       </c>
       <c r="E76">
-        <v>-15.01397651017836</v>
+        <v>-18.37668998252815</v>
       </c>
       <c r="F76">
-        <v>-0.3915188784735655</v>
+        <v>-1.584673412930153</v>
       </c>
       <c r="G76">
-        <v>-4.445361974255213</v>
+        <v>-7.320766097299056</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.10052556901716</v>
       </c>
       <c r="E77">
-        <v>-17.17218382359795</v>
+        <v>-16.76600234747996</v>
       </c>
       <c r="F77">
-        <v>0.05824489112870262</v>
+        <v>-1.477719417636865</v>
       </c>
       <c r="G77">
-        <v>-4.649986794037565</v>
+        <v>-9.570798236337954</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.01651522489541</v>
       </c>
       <c r="E78">
-        <v>-15.44183126289707</v>
+        <v>-17.67828607869519</v>
       </c>
       <c r="F78">
-        <v>-0.5259533388115585</v>
+        <v>-1.547736639864358</v>
       </c>
       <c r="G78">
-        <v>-4.08052992419091</v>
+        <v>-6.496009887100425</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.91801062320495</v>
       </c>
       <c r="E79">
-        <v>-17.40720709612203</v>
+        <v>-19.43947754738831</v>
       </c>
       <c r="F79">
-        <v>-0.1878796370426996</v>
+        <v>-1.505184837475374</v>
       </c>
       <c r="G79">
-        <v>-4.395650822437516</v>
+        <v>-5.093854808306427</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.81303348190263</v>
       </c>
       <c r="E80">
-        <v>-17.54974081551346</v>
+        <v>-17.25951544483587</v>
       </c>
       <c r="F80">
-        <v>-0.382810079644564</v>
+        <v>-2.238215790083845</v>
       </c>
       <c r="G80">
-        <v>-4.337252799124773</v>
+        <v>-6.752908220947869</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.70020732139978</v>
       </c>
       <c r="E81">
-        <v>-18.68190007369712</v>
+        <v>-19.40955339114562</v>
       </c>
       <c r="F81">
-        <v>-0.6215109863373438</v>
+        <v>-1.515682432135864</v>
       </c>
       <c r="G81">
-        <v>-3.892371757920893</v>
+        <v>-6.753077058770372</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.58278854105145</v>
       </c>
       <c r="E82">
-        <v>-19.11260776504065</v>
+        <v>-21.12865269393744</v>
       </c>
       <c r="F82">
-        <v>-0.4548227713255111</v>
+        <v>-2.05336326007488</v>
       </c>
       <c r="G82">
-        <v>-3.098069256138018</v>
+        <v>-5.02834242262979</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.47115041215194</v>
       </c>
       <c r="E83">
-        <v>-19.52060063076171</v>
+        <v>-17.47960833855667</v>
       </c>
       <c r="F83">
-        <v>-0.5305635067314027</v>
+        <v>-1.593067054281982</v>
       </c>
       <c r="G83">
-        <v>-3.222529215686918</v>
+        <v>-5.899863399116166</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.36593320689634</v>
       </c>
       <c r="E84">
-        <v>-20.31312433837009</v>
+        <v>-22.09010206745395</v>
       </c>
       <c r="F84">
-        <v>-0.8190782992884149</v>
+        <v>-2.329918697411451</v>
       </c>
       <c r="G84">
-        <v>-3.930486068714522</v>
+        <v>-5.471293415784275</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.27729844016516</v>
       </c>
       <c r="E85">
-        <v>-20.97315848193606</v>
+        <v>-22.86149138686854</v>
       </c>
       <c r="F85">
-        <v>-0.6489162253510657</v>
+        <v>-1.993579945472956</v>
       </c>
       <c r="G85">
-        <v>-3.76356174153339</v>
+        <v>-5.374307673665786</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.20836480632933</v>
       </c>
       <c r="E86">
-        <v>-22.85663686273231</v>
+        <v>-23.36573243914862</v>
       </c>
       <c r="F86">
-        <v>-0.6581832805152596</v>
+        <v>-2.581674091965198</v>
       </c>
       <c r="G86">
-        <v>-2.613911902656224</v>
+        <v>-4.792946082059912</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.1657147608844</v>
       </c>
       <c r="E87">
-        <v>-23.13146995025783</v>
+        <v>-23.68247202514112</v>
       </c>
       <c r="F87">
-        <v>-0.7593820885118404</v>
+        <v>-2.455333160708059</v>
       </c>
       <c r="G87">
-        <v>-2.806181766486016</v>
+        <v>-6.398242856234668</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.1594915261189</v>
       </c>
       <c r="E88">
-        <v>-25.38145131791686</v>
+        <v>-24.38931247605037</v>
       </c>
       <c r="F88">
-        <v>-1.168217354288449</v>
+        <v>-2.336278860367856</v>
       </c>
       <c r="G88">
-        <v>-2.554196282218851</v>
+        <v>-5.974708212668009</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.18752630600054</v>
       </c>
       <c r="E89">
-        <v>-26.3265076155256</v>
+        <v>-25.98393761379335</v>
       </c>
       <c r="F89">
-        <v>-1.455294141874242</v>
+        <v>-2.082405259152209</v>
       </c>
       <c r="G89">
-        <v>-3.354831857618352</v>
+        <v>-5.831543670822226</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.25021753485774</v>
       </c>
       <c r="E90">
-        <v>-26.19209345002993</v>
+        <v>-27.62392447567117</v>
       </c>
       <c r="F90">
-        <v>-1.10301855730868</v>
+        <v>-2.622108479545241</v>
       </c>
       <c r="G90">
-        <v>-2.850874131266177</v>
+        <v>-4.423462715512934</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.35013301330944</v>
       </c>
       <c r="E91">
-        <v>-28.43637799738731</v>
+        <v>-30.64180370928488</v>
       </c>
       <c r="F91">
-        <v>-1.424481559583453</v>
+        <v>-3.191131639403761</v>
       </c>
       <c r="G91">
-        <v>-3.308454425158701</v>
+        <v>-4.812153867278764</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.47681104579907</v>
       </c>
       <c r="E92">
-        <v>-29.68125323785889</v>
+        <v>-30.37189986571671</v>
       </c>
       <c r="F92">
-        <v>-1.875849623278061</v>
+        <v>-3.086766211429259</v>
       </c>
       <c r="G92">
-        <v>-2.433523586766877</v>
+        <v>-5.642445309619056</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.6256558767157</v>
       </c>
       <c r="E93">
-        <v>-31.61507239996141</v>
+        <v>-32.94109789465043</v>
       </c>
       <c r="F93">
-        <v>-1.940310413301235</v>
+        <v>-3.426376107936094</v>
       </c>
       <c r="G93">
-        <v>-3.175747896671477</v>
+        <v>-5.823508976798415</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.77994881701318</v>
       </c>
       <c r="E94">
-        <v>-34.80253166397734</v>
+        <v>-33.87658099820696</v>
       </c>
       <c r="F94">
-        <v>-2.028862537710074</v>
+        <v>-2.952691252334071</v>
       </c>
       <c r="G94">
-        <v>-3.503429004694078</v>
+        <v>-6.059140366101581</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.92736335618019</v>
       </c>
       <c r="E95">
-        <v>-35.47286129319975</v>
+        <v>-37.35091456213481</v>
       </c>
       <c r="F95">
-        <v>-2.161734672162486</v>
+        <v>-3.615033491406903</v>
       </c>
       <c r="G95">
-        <v>-4.247523772828367</v>
+        <v>-6.998338825047278</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.05789747969995</v>
       </c>
       <c r="E96">
-        <v>-37.91970448292023</v>
+        <v>-37.19083074172666</v>
       </c>
       <c r="F96">
-        <v>-2.539837332797034</v>
+        <v>-3.205389743760462</v>
       </c>
       <c r="G96">
-        <v>-4.070343375566573</v>
+        <v>-5.975903319607686</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.1547955064721</v>
       </c>
       <c r="E97">
-        <v>-40.23033117448998</v>
+        <v>-41.69389548173998</v>
       </c>
       <c r="F97">
-        <v>-2.820277600744179</v>
+        <v>-4.7644714077737</v>
       </c>
       <c r="G97">
-        <v>-4.870091724761549</v>
+        <v>-6.471558197747368</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.20681913728024</v>
       </c>
       <c r="E98">
-        <v>-42.18721838318757</v>
+        <v>-43.45949541987956</v>
       </c>
       <c r="F98">
-        <v>-3.349817388424878</v>
+        <v>-3.946793749543862</v>
       </c>
       <c r="G98">
-        <v>-4.393892922756163</v>
+        <v>-7.750120679923754</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.21635322088477</v>
       </c>
       <c r="E99">
-        <v>-44.38860016779628</v>
+        <v>-45.6227519818177</v>
       </c>
       <c r="F99">
-        <v>-3.367333967702596</v>
+        <v>-4.708038423035887</v>
       </c>
       <c r="G99">
-        <v>-4.536057679849086</v>
+        <v>-6.504355772404927</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.17449029407528</v>
       </c>
       <c r="E100">
-        <v>-45.96953346437708</v>
+        <v>-46.72817060098606</v>
       </c>
       <c r="F100">
-        <v>-3.375178063101768</v>
+        <v>-4.589589890208341</v>
       </c>
       <c r="G100">
-        <v>-5.684820292521727</v>
+        <v>-8.139987075356025</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.0990212822026</v>
       </c>
       <c r="E101">
-        <v>-48.52695180029835</v>
+        <v>-49.03662928562465</v>
       </c>
       <c r="F101">
-        <v>-3.905854951629752</v>
+        <v>-4.355776299970607</v>
       </c>
       <c r="G101">
-        <v>-5.691014323225704</v>
+        <v>-8.413252746349626</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.9842440283329</v>
       </c>
       <c r="E102">
-        <v>-51.11900616966729</v>
+        <v>-50.92679395829322</v>
       </c>
       <c r="F102">
-        <v>-4.050544699623174</v>
+        <v>-4.69781401764581</v>
       </c>
       <c r="G102">
-        <v>-6.754950827545599</v>
+        <v>-8.08536307395805</v>
       </c>
     </row>
   </sheetData>
